--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -262,7 +262,7 @@
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29 08:05:58</t>
+    <t xml:space="preserve">2026-07-31 09:26:31</t>
   </si>
 </sst>
 </file>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -262,7 +262,7 @@
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-31 09:26:31</t>
+    <t xml:space="preserve">2026-08-01 08:21:19</t>
   </si>
 </sst>
 </file>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -262,7 +262,7 @@
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-01 08:21:19</t>
+    <t xml:space="preserve">2026-08-01 08:42:52</t>
   </si>
 </sst>
 </file>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -262,7 +262,7 @@
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-01 08:42:52</t>
+    <t xml:space="preserve">2026-08-01 09:26:43</t>
   </si>
 </sst>
 </file>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -256,13 +256,13 @@
     <t xml:space="preserve">NRL</t>
   </si>
   <si>
-    <t xml:space="preserve">conservative_fallback_until_four_real_weekly_snapshots</t>
+    <t xml:space="preserve">robust_week_to_week_production_rating_volatility</t>
   </si>
   <si>
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-01 09:26:43</t>
+    <t xml:space="preserve">2026-08-03 19:28:59</t>
   </si>
 </sst>
 </file>
@@ -682,7 +682,7 @@
         <v>0.4</v>
       </c>
       <c r="I2" t="n">
-        <v>235.29</v>
+        <v>229.89</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -697,22 +697,22 @@
         <v>#NUM!</v>
       </c>
       <c r="N2" t="n">
-        <v>80</v>
+        <v>80.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>51.1</v>
+        <v>51.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
-        <v>29.4</v>
+        <v>29.9</v>
       </c>
       <c r="S2" t="n">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="3">
@@ -732,16 +732,16 @@
         <v>16.4</v>
       </c>
       <c r="F3" t="n">
-        <v>91.3</v>
+        <v>91.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H3" t="n">
-        <v>8.7</v>
+        <v>8.4</v>
       </c>
       <c r="I3" t="n">
-        <v>11.49</v>
+        <v>11.92</v>
       </c>
       <c r="J3" t="n">
         <v>99.9</v>
@@ -756,22 +756,22 @@
         <v>1052.63</v>
       </c>
       <c r="N3" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="O3" t="n">
-        <v>8.06</v>
+        <v>8.24</v>
       </c>
       <c r="P3" t="n">
-        <v>41.4</v>
+        <v>42.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="R3" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="S3" t="n">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="4">
@@ -791,46 +791,46 @@
         <v>15.7</v>
       </c>
       <c r="F4" t="n">
-        <v>78.2</v>
+        <v>78.8</v>
       </c>
       <c r="G4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H4" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.58</v>
+        <v>4.71</v>
       </c>
       <c r="J4" t="n">
-        <v>99.2</v>
+        <v>99.4</v>
       </c>
       <c r="K4" t="n">
         <v>1.01</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>130.72</v>
+        <v>153.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>42.11</v>
+        <v>44.84</v>
       </c>
       <c r="P4" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R4" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="S4" t="n">
-        <v>5.26</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="5">
@@ -853,13 +853,13 @@
         <v>68.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H5" t="n">
         <v>31.3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
         <v>99.3</v>
@@ -871,25 +871,25 @@
         <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>141.84</v>
+        <v>148.15</v>
       </c>
       <c r="N5" t="n">
         <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>20.26</v>
+        <v>20.41</v>
       </c>
       <c r="P5" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="R5" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="S5" t="n">
-        <v>8.63</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="6">
@@ -909,46 +909,46 @@
         <v>14.7</v>
       </c>
       <c r="F6" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="H6" t="n">
-        <v>62.7</v>
+        <v>63</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J6" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="K6" t="n">
         <v>1.03</v>
       </c>
       <c r="L6" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
-        <v>36.1</v>
+        <v>36.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O6" t="n">
-        <v>487.8</v>
+        <v>689.66</v>
       </c>
       <c r="P6" t="n">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.35</v>
+        <v>5.47</v>
       </c>
       <c r="R6" t="n">
-        <v>8.2</v>
+        <v>8.1</v>
       </c>
       <c r="S6" t="n">
-        <v>12.12</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="7">
@@ -968,13 +968,13 @@
         <v>14.1</v>
       </c>
       <c r="F7" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="G7" t="n">
-        <v>7.65</v>
+        <v>7.73</v>
       </c>
       <c r="H7" t="n">
-        <v>86.9</v>
+        <v>87.1</v>
       </c>
       <c r="I7" t="n">
         <v>1.15</v>
@@ -989,25 +989,25 @@
         <v>11.1</v>
       </c>
       <c r="M7" t="n">
-        <v>9.03</v>
+        <v>9.02</v>
       </c>
       <c r="N7" t="n">
         <v>0.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1818.18</v>
+        <v>1538.46</v>
       </c>
       <c r="P7" t="n">
-        <v>8.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.38</v>
+        <v>11.79</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="S7" t="n">
-        <v>27.06</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="8">
@@ -1027,28 +1027,28 @@
         <v>12.8</v>
       </c>
       <c r="F8" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="G8" t="n">
-        <v>17.64</v>
+        <v>18.52</v>
       </c>
       <c r="H8" t="n">
-        <v>94.3</v>
+        <v>94.6</v>
       </c>
       <c r="I8" t="n">
         <v>1.06</v>
       </c>
       <c r="J8" t="n">
-        <v>67.4</v>
+        <v>67.5</v>
       </c>
       <c r="K8" t="n">
         <v>1.48</v>
       </c>
       <c r="L8" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P8" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.65</v>
+        <v>15.92</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="S8" t="n">
-        <v>33.61</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="9">
@@ -1086,25 +1086,25 @@
         <v>12.2</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>35.52</v>
+        <v>36.63</v>
       </c>
       <c r="H9" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="I9" t="n">
         <v>1.03</v>
       </c>
       <c r="J9" t="n">
-        <v>57</v>
+        <v>56.8</v>
       </c>
       <c r="K9" t="n">
         <v>1.76</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="M9" t="n">
         <v>2.32</v>
@@ -1116,16 +1116,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.21</v>
+        <v>16.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="S9" t="n">
-        <v>35.09</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="10">
@@ -1145,28 +1145,28 @@
         <v>13.4</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>30.12</v>
+        <v>30.77</v>
       </c>
       <c r="H10" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="I10" t="n">
         <v>1.03</v>
       </c>
       <c r="J10" t="n">
-        <v>72.4</v>
+        <v>72.7</v>
       </c>
       <c r="K10" t="n">
         <v>1.38</v>
       </c>
       <c r="L10" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1175,16 +1175,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>24.75</v>
+        <v>25.81</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>66.89</v>
+        <v>72.46</v>
       </c>
     </row>
     <row r="11">
@@ -1216,16 +1216,16 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="K11" t="n">
-        <v>14.33</v>
+        <v>14.58</v>
       </c>
       <c r="L11" t="n">
-        <v>93</v>
+        <v>93.1</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1234,16 +1234,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>294.12</v>
+        <v>416.67</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="S11" t="n">
-        <v>645.16</v>
+        <v>909.09</v>
       </c>
     </row>
     <row r="12">
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2500</v>
+        <v>2857.14</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1278,7 +1278,7 @@
         <v>6.8</v>
       </c>
       <c r="K12" t="n">
-        <v>14.7</v>
+        <v>14.81</v>
       </c>
       <c r="L12" t="n">
         <v>93.2</v>
@@ -1296,13 +1296,13 @@
         <v>0.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>454.55</v>
+        <v>500</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="13">
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1334,16 +1334,16 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>22.52</v>
+        <v>23.89</v>
       </c>
       <c r="L13" t="n">
-        <v>95.6</v>
+        <v>95.8</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2500</v>
+        <v>2857.14</v>
       </c>
     </row>
     <row r="14">
@@ -1413,8 +1413,8 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="e">
-        <v>#NUM!</v>
+      <c r="Q14" t="n">
+        <v>20000</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         <v>0.2</v>
       </c>
       <c r="K15" t="n">
-        <v>588.24</v>
+        <v>625</v>
       </c>
       <c r="L15" t="n">
         <v>99.8</v>
@@ -1514,7 +1514,7 @@
         <v>0.1</v>
       </c>
       <c r="K16" t="n">
-        <v>1111.11</v>
+        <v>1428.57</v>
       </c>
       <c r="L16" t="n">
         <v>99.9</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3333.33</v>
+        <v>4000</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
@@ -3316,7 +3316,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="N2" t="n">
         <v>0.98</v>
@@ -3325,7 +3325,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q2" t="s">
         <v>81</v>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -262,7 +262,7 @@
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-03 19:28:59</t>
+    <t xml:space="preserve">2026-08-03 20:19:42</t>
   </si>
 </sst>
 </file>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -79,24 +79,24 @@
     <t xml:space="preserve">Penrith Panthers</t>
   </si>
   <si>
+    <t xml:space="preserve">cronullasharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cronulla Sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydneyroosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Roosters</t>
+  </si>
+  <si>
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">New Zealand Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">cronullasharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cronulla Sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydneyroosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydney Roosters</t>
-  </si>
-  <si>
     <t xml:space="preserve">dolphins</t>
   </si>
   <si>
@@ -121,28 +121,34 @@
     <t xml:space="preserve">Manly Sea Eagles</t>
   </si>
   <si>
+    <t xml:space="preserve">canterburybulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canterbury Bulldogs</t>
+  </si>
+  <si>
     <t xml:space="preserve">nqcowboys</t>
   </si>
   <si>
     <t xml:space="preserve">NQ Cowboys</t>
   </si>
   <si>
+    <t xml:space="preserve">canberraraiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canberra Raiders</t>
+  </si>
+  <si>
     <t xml:space="preserve">melbournestorm</t>
   </si>
   <si>
     <t xml:space="preserve">Melbourne Storm</t>
   </si>
   <si>
-    <t xml:space="preserve">canterburybulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canterbury Bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberraraiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canberra Raiders</t>
+    <t xml:space="preserve">parramattaeels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parramatta Eels</t>
   </si>
   <si>
     <t xml:space="preserve">weststigers</t>
@@ -151,24 +157,18 @@
     <t xml:space="preserve">Wests Tigers</t>
   </si>
   <si>
+    <t xml:space="preserve">goldcoasttitans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Coast Titans</t>
+  </si>
+  <si>
     <t xml:space="preserve">brisbanebroncos</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
   </si>
   <si>
-    <t xml:space="preserve">parramattaeels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parramatta Eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldcoasttitans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Coast Titans</t>
-  </si>
-  <si>
     <t xml:space="preserve">stgeorgeillawarradragons</t>
   </si>
   <si>
@@ -262,7 +262,7 @@
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-03 20:19:42</t>
+    <t xml:space="preserve">2026-08-04 21:38:08</t>
   </si>
 </sst>
 </file>
@@ -664,25 +664,25 @@
         <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="F2" t="n">
-        <v>99.6</v>
+        <v>99.9</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>229.89</v>
+        <v>833.33</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -697,22 +697,22 @@
         <v>#NUM!</v>
       </c>
       <c r="N2" t="n">
-        <v>80.5</v>
+        <v>81.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>51.9</v>
+        <v>47.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="R2" t="n">
-        <v>29.9</v>
+        <v>26.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.34</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="3">
@@ -723,55 +723,55 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>16.4</v>
+        <v>16.9</v>
       </c>
       <c r="E3" t="n">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="F3" t="n">
-        <v>91.6</v>
+        <v>95.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>11.92</v>
+        <v>22.88</v>
       </c>
       <c r="J3" t="n">
-        <v>99.9</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1052.63</v>
+        <v>0</v>
+      </c>
+      <c r="M3" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="N3" t="n">
-        <v>12.1</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>8.24</v>
+        <v>26.88</v>
       </c>
       <c r="P3" t="n">
-        <v>42.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="R3" t="n">
-        <v>21.3</v>
+        <v>24.1</v>
       </c>
       <c r="S3" t="n">
-        <v>4.68</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="4">
@@ -782,55 +782,55 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>15.8</v>
+        <v>17.2</v>
       </c>
       <c r="E4" t="n">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="F4" t="n">
-        <v>78.8</v>
+        <v>94.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="H4" t="n">
-        <v>21.2</v>
+        <v>5.8</v>
       </c>
       <c r="I4" t="n">
-        <v>4.71</v>
+        <v>17.35</v>
       </c>
       <c r="J4" t="n">
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>153.85</v>
+        <v>0</v>
+      </c>
+      <c r="M4" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>11.8</v>
       </c>
       <c r="O4" t="n">
-        <v>44.84</v>
+        <v>8.45</v>
       </c>
       <c r="P4" t="n">
-        <v>36.5</v>
+        <v>39.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="R4" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="S4" t="n">
-        <v>5.28</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="5">
@@ -841,55 +841,55 @@
         <v>26</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="E5" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="F5" t="n">
-        <v>68.7</v>
+        <v>84.9</v>
       </c>
       <c r="G5" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="H5" t="n">
-        <v>31.3</v>
+        <v>15.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>6.62</v>
       </c>
       <c r="J5" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>148.15</v>
+        <v>4000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>20.41</v>
+        <v>33.5</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>36.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>11.4</v>
+        <v>17.8</v>
       </c>
       <c r="S5" t="n">
-        <v>8.74</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="6">
@@ -900,55 +900,55 @@
         <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>20.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.71</v>
+        <v>4.89</v>
       </c>
       <c r="H6" t="n">
-        <v>63</v>
+        <v>79.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="J6" t="n">
-        <v>97.3</v>
+        <v>99.2</v>
       </c>
       <c r="K6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>36.9</v>
+        <v>127.39</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>689.66</v>
+        <v>10000</v>
       </c>
       <c r="P6" t="n">
-        <v>18.3</v>
+        <v>13.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.47</v>
+        <v>7.5</v>
       </c>
       <c r="R6" t="n">
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="S6" t="n">
-        <v>12.32</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="7">
@@ -959,7 +959,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>14.1</v>
@@ -968,46 +968,46 @@
         <v>14.1</v>
       </c>
       <c r="F7" t="n">
-        <v>12.9</v>
+        <v>4.4</v>
       </c>
       <c r="G7" t="n">
-        <v>7.73</v>
+        <v>22.75</v>
       </c>
       <c r="H7" t="n">
-        <v>87.1</v>
+        <v>95.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="J7" t="n">
-        <v>88.9</v>
+        <v>95.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="L7" t="n">
-        <v>11.1</v>
+        <v>4.7</v>
       </c>
       <c r="M7" t="n">
-        <v>9.02</v>
+        <v>21.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1538.46</v>
+        <v>0</v>
+      </c>
+      <c r="O7" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="P7" t="n">
-        <v>8.5</v>
+        <v>8.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.79</v>
+        <v>12.14</v>
       </c>
       <c r="R7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="S7" t="n">
-        <v>29.2</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="8">
@@ -1018,37 +1018,37 @@
         <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="E8" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="F8" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="G8" t="n">
-        <v>18.52</v>
+        <v>263.16</v>
       </c>
       <c r="H8" t="n">
-        <v>94.6</v>
+        <v>99.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>67.5</v>
+        <v>64.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="L8" t="n">
-        <v>32.5</v>
+        <v>35.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P8" t="n">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.92</v>
+        <v>23.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>38.1</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="9">
@@ -1080,34 +1080,34 @@
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="E9" t="n">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>36.63</v>
+        <v>2857.14</v>
       </c>
       <c r="H9" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>56.8</v>
+        <v>32.3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.76</v>
+        <v>3.09</v>
       </c>
       <c r="L9" t="n">
-        <v>43.2</v>
+        <v>67.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2.32</v>
+        <v>1.48</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1116,16 +1116,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P9" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.85</v>
+        <v>51.15</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="S9" t="n">
-        <v>38.1</v>
+        <v>137.93</v>
       </c>
     </row>
     <row r="10">
@@ -1139,34 +1139,34 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>13.4</v>
+        <v>12.3</v>
       </c>
       <c r="E10" t="n">
-        <v>13.4</v>
+        <v>12.3</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>30.77</v>
+        <v>4000</v>
       </c>
       <c r="H10" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>72.7</v>
+        <v>39.5</v>
       </c>
       <c r="K10" t="n">
-        <v>1.38</v>
+        <v>2.53</v>
       </c>
       <c r="L10" t="n">
-        <v>27.3</v>
+        <v>60.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.67</v>
+        <v>1.65</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1175,16 +1175,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P10" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>25.81</v>
+        <v>65.15</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="S10" t="n">
-        <v>72.46</v>
+        <v>212.77</v>
       </c>
     </row>
     <row r="11">
@@ -1195,37 +1195,37 @@
         <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10.6</v>
+        <v>13.1</v>
       </c>
       <c r="E11" t="n">
-        <v>10.6</v>
+        <v>13.1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G11" t="n">
-        <v>10000</v>
+        <v>1176.47</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>99.9</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>6.9</v>
+        <v>61.9</v>
       </c>
       <c r="K11" t="n">
-        <v>14.58</v>
+        <v>1.61</v>
       </c>
       <c r="L11" t="n">
-        <v>93.1</v>
+        <v>38.1</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>2.63</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1234,16 +1234,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>416.67</v>
+        <v>79.05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="S11" t="n">
-        <v>909.09</v>
+        <v>256.41</v>
       </c>
     </row>
     <row r="12">
@@ -1254,19 +1254,19 @@
         <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="E12" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
-        <v>2857.14</v>
+      <c r="G12" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1275,13 +1275,13 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="K12" t="n">
-        <v>14.81</v>
+        <v>14.88</v>
       </c>
       <c r="L12" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -1293,16 +1293,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>500</v>
+        <v>357.14</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="S12" t="n">
-        <v>2500</v>
+        <v>769.23</v>
       </c>
     </row>
     <row r="13">
@@ -1316,16 +1316,16 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="E13" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="n">
-        <v>20000</v>
+      <c r="G13" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1334,16 +1334,16 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>23.89</v>
+        <v>259.74</v>
       </c>
       <c r="L13" t="n">
-        <v>95.8</v>
+        <v>99.6</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1352,16 +1352,16 @@
         <v>#NUM!</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>689.66</v>
+        <v>6666.67</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2857.14</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="14">
@@ -1375,10 +1375,10 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1393,13 +1393,13 @@
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1176.47</v>
+        <v>3333.33</v>
       </c>
       <c r="L14" t="n">
-        <v>99.9</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -1413,8 +1413,8 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>20000</v>
+      <c r="Q14" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1431,13 +1431,13 @@
         <v>46</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="E15" t="n">
-        <v>8.7</v>
+        <v>8.1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>625</v>
+        <v>0</v>
+      </c>
+      <c r="K15" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="L15" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -1493,10 +1493,10 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="E16" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1511,13 +1511,13 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1428.57</v>
+        <v>20000</v>
       </c>
       <c r="L16" t="n">
-        <v>99.9</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1549,13 +1549,13 @@
         <v>50</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="E17" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
@@ -1611,10 +1611,10 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="E18" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1704,26 +1704,26 @@
         <v>2026</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46226</v>
+        <v>46240</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
         <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
-        <v>-11.6856155716015</v>
+        <v>0.604232347309297</v>
       </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1731,26 +1731,26 @@
         <v>2026</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46227</v>
+        <v>46241</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.926375642891134</v>
+        <v>-1.2927300146588</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -1758,26 +1758,26 @@
         <v>2026</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46227</v>
+        <v>46241</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H4" t="n">
-        <v>4.16705889731936</v>
+        <v>7.3954803250696</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -1785,26 +1785,26 @@
         <v>2026</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46228</v>
+        <v>46242</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
         <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
         <v>41</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H5" t="n">
-        <v>6.89766674820381</v>
+        <v>-2.12333666651239</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -1812,26 +1812,26 @@
         <v>2026</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46228</v>
+        <v>46242</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.11537576490978</v>
+        <v>8.3779907781502</v>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -1839,26 +1839,26 @@
         <v>2026</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46228</v>
+        <v>46242</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H7" t="n">
-        <v>4.47873443392286</v>
+        <v>6.560825396377</v>
       </c>
       <c r="I7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -1866,26 +1866,26 @@
         <v>2026</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46229</v>
+        <v>46243</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.28350116678589</v>
+        <v>-1.93292222662929</v>
       </c>
       <c r="I8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1893,26 +1893,26 @@
         <v>2026</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46229</v>
+        <v>46243</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-14.3269599345938</v>
+      </c>
+      <c r="I9" t="n">
         <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-1.1856274083587</v>
-      </c>
-      <c r="I9" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1920,26 +1920,26 @@
         <v>2026</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46233</v>
+        <v>46247</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.68599208399296</v>
+        <v>1.99716640862105</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -1947,26 +1947,26 @@
         <v>2026</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46234</v>
+        <v>46248</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
       </c>
       <c r="H11" t="n">
-        <v>-8.57309493481628</v>
+        <v>-1.19069442887577</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -1974,26 +1974,26 @@
         <v>2026</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46234</v>
+        <v>46248</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H12" t="n">
-        <v>3.17478222867258</v>
+        <v>-1.82010015473468</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -2001,26 +2001,26 @@
         <v>2026</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.60331646093084</v>
+        <v>8.4750007341986</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -2028,26 +2028,26 @@
         <v>2026</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H14" t="n">
-        <v>10.7551174854701</v>
+        <v>-0.458186305114447</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -2055,26 +2055,26 @@
         <v>2026</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.55688540390886</v>
+        <v>-10.6909715838456</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -2082,26 +2082,26 @@
         <v>2026</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46236</v>
+        <v>46250</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H16" t="n">
-        <v>4.91703074010802</v>
+        <v>5.95878676186548</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -2109,26 +2109,26 @@
         <v>2026</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46236</v>
+        <v>46250</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.604237719840717</v>
+        <v>-1.09663549706416</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2136,26 +2136,26 @@
         <v>2026</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46240</v>
+        <v>46254</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.844903098706256</v>
+        <v>-8.57115002734572</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -2163,26 +2163,26 @@
         <v>2026</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46241</v>
+        <v>46255</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.513272535248708</v>
+        <v>5.00287295033556</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -2190,26 +2190,26 @@
         <v>2026</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46241</v>
+        <v>46255</v>
       </c>
       <c r="C20"/>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.05054898757375</v>
+      </c>
+      <c r="I20" t="n">
         <v>25</v>
-      </c>
-      <c r="G20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" t="n">
-        <v>7.0651526933519</v>
-      </c>
-      <c r="I20" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -2217,26 +2217,26 @@
         <v>2026</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46242</v>
+        <v>46256</v>
       </c>
       <c r="C21"/>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
         <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G21" t="s">
         <v>33</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.53553128683703</v>
+        <v>0.987054911392908</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -2244,26 +2244,26 @@
         <v>2026</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46242</v>
+        <v>46256</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H22" t="n">
-        <v>8.58269236768908</v>
+        <v>-4.21555642479302</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -2271,26 +2271,26 @@
         <v>2026</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46242</v>
+        <v>46256</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="H23" t="n">
-        <v>8.71734292631914</v>
+        <v>-5.91725328227839</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
@@ -2298,26 +2298,26 @@
         <v>2026</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46243</v>
+        <v>46257</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.22084982242487</v>
+        <v>-10.8494571578315</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -2325,26 +2325,26 @@
         <v>2026</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46243</v>
+        <v>46257</v>
       </c>
       <c r="C25"/>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H25" t="n">
-        <v>-11.0081155222332</v>
+        <v>15.2350731602138</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -2352,26 +2352,26 @@
         <v>2026</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46247</v>
+        <v>46261</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E26" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" t="s">
+        <v>41</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.41255157115872</v>
+      </c>
+      <c r="I26" t="n">
         <v>26</v>
-      </c>
-      <c r="F26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" t="n">
-        <v>5.92642654903824</v>
-      </c>
-      <c r="I26" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -2379,26 +2379,26 @@
         <v>2026</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="s">
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="H27" t="n">
-        <v>1.24939317905819</v>
+        <v>8.86208665513571</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -2406,26 +2406,26 @@
         <v>2026</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G28" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H28" t="n">
-        <v>-3.3196429193182</v>
+        <v>8.97979470578982</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -2433,26 +2433,26 @@
         <v>2026</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46249</v>
+        <v>46263</v>
       </c>
       <c r="C29"/>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="G29" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H29" t="n">
-        <v>8.68167737362197</v>
+        <v>-4.6727026881516</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -2460,26 +2460,26 @@
         <v>2026</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46249</v>
+        <v>46263</v>
       </c>
       <c r="C30"/>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F30" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="G30" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.07319693857031</v>
+        <v>3.67280455123735</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -2487,26 +2487,26 @@
         <v>2026</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46249</v>
+        <v>46263</v>
       </c>
       <c r="C31"/>
       <c r="D31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" t="s">
         <v>46</v>
       </c>
-      <c r="E31" t="s">
-        <v>22</v>
-      </c>
       <c r="F31" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" t="s">
         <v>45</v>
       </c>
-      <c r="G31" t="s">
-        <v>21</v>
-      </c>
       <c r="H31" t="n">
-        <v>-8.55568232503162</v>
+        <v>5.20846201021966</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -2514,26 +2514,26 @@
         <v>2026</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46250</v>
+        <v>46264</v>
       </c>
       <c r="C32"/>
       <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
         <v>30</v>
       </c>
-      <c r="E32" t="s">
-        <v>50</v>
-      </c>
       <c r="F32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
         <v>29</v>
       </c>
-      <c r="G32" t="s">
-        <v>49</v>
-      </c>
       <c r="H32" t="n">
-        <v>5.28598501092391</v>
+        <v>4.58088046268246</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
@@ -2541,26 +2541,26 @@
         <v>2026</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46250</v>
+        <v>46264</v>
       </c>
       <c r="C33"/>
       <c r="D33" t="s">
         <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F33" t="s">
         <v>43</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H33" t="n">
-        <v>0.791702342639036</v>
+        <v>-11.9118758102552</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -2568,26 +2568,26 @@
         <v>2026</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46254</v>
+        <v>46268</v>
       </c>
       <c r="C34"/>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H34" t="n">
-        <v>-7.13533154260174</v>
+        <v>4.65531500431795</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
@@ -2595,26 +2595,26 @@
         <v>2026</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46255</v>
+        <v>46269</v>
       </c>
       <c r="C35"/>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F35" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G35" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H35" t="n">
-        <v>3.6767683170419</v>
+        <v>-6.16242627934834</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -2622,26 +2622,26 @@
         <v>2026</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46255</v>
+        <v>46269</v>
       </c>
       <c r="C36"/>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-4.33682408663243</v>
+      </c>
+      <c r="I36" t="n">
         <v>27</v>
-      </c>
-      <c r="G36" t="s">
-        <v>47</v>
-      </c>
-      <c r="H36" t="n">
-        <v>9.85862034345235</v>
-      </c>
-      <c r="I36" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="37">
@@ -2649,26 +2649,26 @@
         <v>2026</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46256</v>
+        <v>46270</v>
       </c>
       <c r="C37"/>
       <c r="D37" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
         <v>34</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G37" t="s">
         <v>33</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.912269200606755</v>
+        <v>5.15508334617454</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
@@ -2676,26 +2676,26 @@
         <v>2026</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46256</v>
+        <v>46270</v>
       </c>
       <c r="C38"/>
       <c r="D38" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G38" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.45500011003367</v>
+        <v>-2.97868877094217</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
@@ -2703,26 +2703,26 @@
         <v>2026</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46256</v>
+        <v>46270</v>
       </c>
       <c r="C39"/>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F39" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G39" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.77144186280695</v>
+        <v>9.23961805757377</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
@@ -2730,26 +2730,26 @@
         <v>2026</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46257</v>
+        <v>46271</v>
       </c>
       <c r="C40"/>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H40" t="n">
-        <v>-7.38388161988936</v>
+        <v>-2.00223209643773</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
@@ -2757,457 +2757,25 @@
         <v>2026</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46257</v>
+        <v>46271</v>
       </c>
       <c r="C41"/>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H41" t="n">
-        <v>11.7263576846356</v>
+        <v>16.819387540934</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C42"/>
-      <c r="D42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E42" t="s">
-        <v>38</v>
-      </c>
-      <c r="F42" t="s">
-        <v>45</v>
-      </c>
-      <c r="G42" t="s">
-        <v>37</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-1.93362331767858</v>
-      </c>
-      <c r="I42" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="C43"/>
-      <c r="D43" t="s">
-        <v>34</v>
-      </c>
-      <c r="E43" t="s">
-        <v>52</v>
-      </c>
-      <c r="F43" t="s">
-        <v>33</v>
-      </c>
-      <c r="G43" t="s">
-        <v>51</v>
-      </c>
-      <c r="H43" t="n">
-        <v>11.1632208494324</v>
-      </c>
-      <c r="I43" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="C44"/>
-      <c r="D44" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" t="s">
-        <v>39</v>
-      </c>
-      <c r="H44" t="n">
-        <v>11.6508465068322</v>
-      </c>
-      <c r="I44" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B45" s="1" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C45"/>
-      <c r="D45" t="s">
-        <v>50</v>
-      </c>
-      <c r="E45" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" t="s">
-        <v>49</v>
-      </c>
-      <c r="G45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-3.80758361533926</v>
-      </c>
-      <c r="I45" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C46"/>
-      <c r="D46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" t="s">
-        <v>25</v>
-      </c>
-      <c r="G46" t="s">
-        <v>27</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.26349962134257</v>
-      </c>
-      <c r="I46" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C47"/>
-      <c r="D47" t="s">
-        <v>36</v>
-      </c>
-      <c r="E47" t="s">
-        <v>44</v>
-      </c>
-      <c r="F47" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" t="s">
-        <v>43</v>
-      </c>
-      <c r="H47" t="n">
-        <v>7.69963286508477</v>
-      </c>
-      <c r="I47" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C48"/>
-      <c r="D48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" t="s">
-        <v>30</v>
-      </c>
-      <c r="F48" t="s">
-        <v>21</v>
-      </c>
-      <c r="G48" t="s">
-        <v>29</v>
-      </c>
-      <c r="H48" t="n">
-        <v>6.33952965668067</v>
-      </c>
-      <c r="I48" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C49"/>
-      <c r="D49" t="s">
-        <v>48</v>
-      </c>
-      <c r="E49" t="s">
-        <v>24</v>
-      </c>
-      <c r="F49" t="s">
-        <v>47</v>
-      </c>
-      <c r="G49" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-9.61217545975341</v>
-      </c>
-      <c r="I49" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="C50"/>
-      <c r="D50" t="s">
-        <v>40</v>
-      </c>
-      <c r="E50" t="s">
-        <v>46</v>
-      </c>
-      <c r="F50" t="s">
-        <v>39</v>
-      </c>
-      <c r="G50" t="s">
-        <v>45</v>
-      </c>
-      <c r="H50" t="n">
-        <v>2.78103929567975</v>
-      </c>
-      <c r="I50" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C51"/>
-      <c r="D51" t="s">
-        <v>50</v>
-      </c>
-      <c r="E51" t="s">
-        <v>28</v>
-      </c>
-      <c r="F51" t="s">
-        <v>49</v>
-      </c>
-      <c r="G51" t="s">
-        <v>27</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-4.94886103247247</v>
-      </c>
-      <c r="I51" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B52" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C52"/>
-      <c r="D52" t="s">
-        <v>32</v>
-      </c>
-      <c r="E52" t="s">
-        <v>26</v>
-      </c>
-      <c r="F52" t="s">
-        <v>31</v>
-      </c>
-      <c r="G52" t="s">
-        <v>25</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.276688432640039</v>
-      </c>
-      <c r="I52" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B53" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C53"/>
-      <c r="D53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E53" t="s">
-        <v>34</v>
-      </c>
-      <c r="F53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53" t="s">
-        <v>33</v>
-      </c>
-      <c r="H53" t="n">
-        <v>4.086527720516</v>
-      </c>
-      <c r="I53" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B54" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C54"/>
-      <c r="D54" t="s">
-        <v>36</v>
-      </c>
-      <c r="E54" t="s">
-        <v>42</v>
-      </c>
-      <c r="F54" t="s">
-        <v>35</v>
-      </c>
-      <c r="G54" t="s">
-        <v>41</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2.14269885243887</v>
-      </c>
-      <c r="I54" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B55" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C55"/>
-      <c r="D55" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" t="s">
-        <v>38</v>
-      </c>
-      <c r="F55" t="s">
-        <v>23</v>
-      </c>
-      <c r="G55" t="s">
-        <v>37</v>
-      </c>
-      <c r="H55" t="n">
-        <v>7.74335690186947</v>
-      </c>
-      <c r="I55" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B56" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="C56"/>
-      <c r="D56" t="s">
-        <v>52</v>
-      </c>
-      <c r="E56" t="s">
-        <v>48</v>
-      </c>
-      <c r="F56" t="s">
-        <v>51</v>
-      </c>
-      <c r="G56" t="s">
-        <v>47</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-0.0552073269218403</v>
-      </c>
-      <c r="I56" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B57" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="C57"/>
-      <c r="D57" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" t="s">
-        <v>44</v>
-      </c>
-      <c r="F57" t="s">
-        <v>19</v>
-      </c>
-      <c r="G57" t="s">
-        <v>43</v>
-      </c>
-      <c r="H57" t="n">
-        <v>16.312051498116</v>
-      </c>
-      <c r="I57" t="n">
         <v>28</v>
       </c>
     </row>
@@ -3289,19 +2857,19 @@
         <v>20000</v>
       </c>
       <c r="D2" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>1.341</v>
+        <v>0.413</v>
       </c>
       <c r="I2" t="n">
         <v>14.5</v>
@@ -3325,7 +2893,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="Q2" t="s">
         <v>81</v>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -262,7 +262,7 @@
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04 21:38:08</t>
+    <t xml:space="preserve">2026-08-10 20:52:34</t>
   </si>
 </sst>
 </file>
@@ -2893,7 +2893,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="Q2" t="s">
         <v>81</v>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -262,7 +262,7 @@
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-10 20:52:34</t>
+    <t xml:space="preserve">2026-08-10 21:09:51</t>
   </si>
 </sst>
 </file>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -262,7 +262,7 @@
     <t xml:space="preserve">top_8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-10 21:09:51</t>
+    <t xml:space="preserve">2026-08-11 21:00:53</t>
   </si>
 </sst>
 </file>
@@ -2893,7 +2893,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="Q2" t="s">
         <v>81</v>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t xml:space="preserve">Team</t>
   </si>
@@ -35,10 +35,10 @@
     <t xml:space="preserve">Penrith Panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09</t>
+    <t xml:space="preserve">4.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19</t>
   </si>
   <si>
     <t xml:space="preserve">1.00</t>
@@ -47,162 +47,153 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
+    <t xml:space="preserve">New Zealand Warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cronulla Sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19</t>
+    <t xml:space="preserve">5.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48</t>
   </si>
   <si>
     <t xml:space="preserve">1.05</t>
   </si>
   <si>
-    <t xml:space="preserve">Sydney Roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Zealand Warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18</t>
+    <t xml:space="preserve">Dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1333.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Sydney Rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NQ Cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1111.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canterbury Bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manly Sea Eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">689.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canberra Raiders</t>
   </si>
   <si>
     <t xml:space="preserve">4000.00</t>
   </si>
   <si>
-    <t xml:space="preserve">Dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89</t>
+    <t xml:space="preserve">2500.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.11</t>
   </si>
   <si>
     <t xml:space="preserve">1.01</t>
   </si>
   <si>
-    <t xml:space="preserve">127.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Sydney Rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manly Sea Eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2857.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canterbury Bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NQ Cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">256.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1176.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canberra Raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">769.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Melbourne Storm</t>
   </si>
   <si>
@@ -212,7 +203,7 @@
     <t xml:space="preserve">6666.67</t>
   </si>
   <si>
-    <t xml:space="preserve">259.74</t>
+    <t xml:space="preserve">165.29</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
@@ -222,9 +213,6 @@
   </si>
   <si>
     <t xml:space="preserve">Parramatta Eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3333.33</t>
   </si>
   <si>
     <t xml:space="preserve">St. George Illawarra Dragons</t>
@@ -664,172 +652,172 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
         <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
         <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>43</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
         <v>47</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>53</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>54</v>
-      </c>
-      <c r="D11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>58</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12" t="s">
         <v>59</v>
-      </c>
-      <c r="C12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>63</v>
       </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
-        <v>66</v>
-      </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -841,7 +829,7 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -849,7 +837,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -861,7 +849,7 @@
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -869,7 +857,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -881,7 +869,7 @@
         <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
@@ -889,7 +877,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -909,7 +897,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t xml:space="preserve">Team</t>
   </si>
@@ -32,70 +32,67 @@
     <t xml:space="preserve">Miss Top 8 Odds</t>
   </si>
   <si>
+    <t xml:space="preserve">New Zealand Warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
     <t xml:space="preserve">Penrith Panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Zealand Warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06</t>
+    <t xml:space="preserve">4.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43</t>
   </si>
   <si>
     <t xml:space="preserve">Cronulla Sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydney Roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05</t>
+    <t xml:space="preserve">7.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44</t>
   </si>
   <si>
     <t xml:space="preserve">Dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">15.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1333.33</t>
+    <t xml:space="preserve">9.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78</t>
   </si>
   <si>
     <t xml:space="preserve">Newcastle Knights</t>
@@ -104,106 +101,91 @@
     <t xml:space="preserve">25.09</t>
   </si>
   <si>
-    <t xml:space="preserve">10.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.67</t>
+    <t xml:space="preserve">10.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.81</t>
   </si>
   <si>
     <t xml:space="preserve">South Sydney Rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">57.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45</t>
+    <t xml:space="preserve">39.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">444.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.28</t>
   </si>
   <si>
     <t xml:space="preserve">NQ Cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">153.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.08</t>
+    <t xml:space="preserve">194.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canterbury Bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">408.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canberra Raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">689.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melbourne Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2857.14</t>
   </si>
   <si>
     <t xml:space="preserve">1111.11</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canterbury Bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36</t>
+    <t xml:space="preserve">74.07</t>
   </si>
   <si>
     <t xml:space="preserve">Manly Sea Eagles</t>
   </si>
   <si>
-    <t xml:space="preserve">689.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canberra Raiders</t>
-  </si>
-  <si>
     <t xml:space="preserve">4000.00</t>
   </si>
   <si>
-    <t xml:space="preserve">2500.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melbourne Storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20000.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6666.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.29</t>
+    <t xml:space="preserve">50.89</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
@@ -589,50 +571,50 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -649,10 +631,10 @@
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -669,250 +651,250 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
         <v>33</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
         <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
         <v>40</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" t="s">
         <v>45</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" t="s">
         <v>50</v>
-      </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">Team</t>
   </si>
@@ -35,13 +35,10 @@
     <t xml:space="preserve">New Zealand Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02</t>
+    <t xml:space="preserve">3.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03</t>
   </si>
   <si>
     <t xml:space="preserve">1.00</t>
@@ -53,145 +50,121 @@
     <t xml:space="preserve">Penrith Panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01</t>
+    <t xml:space="preserve">4.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43</t>
+    <t xml:space="preserve">5.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08</t>
   </si>
   <si>
     <t xml:space="preserve">Cronulla Sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44</t>
+    <t xml:space="preserve">7.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35</t>
   </si>
   <si>
     <t xml:space="preserve">Dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78</t>
+    <t xml:space="preserve">7.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54</t>
   </si>
   <si>
     <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
-    <t xml:space="preserve">25.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.81</t>
+    <t xml:space="preserve">33.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.48</t>
   </si>
   <si>
     <t xml:space="preserve">South Sydney Rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">39.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">444.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.28</t>
+    <t xml:space="preserve">39.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.46</t>
   </si>
   <si>
     <t xml:space="preserve">NQ Cowboys</t>
   </si>
   <si>
+    <t xml:space="preserve">153.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canterbury Bulldogs</t>
+  </si>
+  <si>
     <t xml:space="preserve">194.17</t>
   </si>
   <si>
-    <t xml:space="preserve">56.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canterbury Bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15</t>
+    <t xml:space="preserve">69.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manly Sea Eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">833.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
   </si>
   <si>
     <t xml:space="preserve">Canberra Raiders</t>
   </si>
   <si>
-    <t xml:space="preserve">689.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10</t>
+    <t xml:space="preserve">Gold Coast Titans</t>
   </si>
   <si>
     <t xml:space="preserve">Melbourne Storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2857.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1111.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manly Sea Eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4000.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Coast Titans</t>
   </si>
   <si>
     <t xml:space="preserve">Parramatta Eels</t>
@@ -571,227 +544,227 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>44</v>
-      </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>46</v>
       </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>49</v>
-      </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -799,102 +772,102 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Team</t>
   </si>
@@ -35,10 +35,10 @@
     <t xml:space="preserve">New Zealand Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03</t>
+    <t xml:space="preserve">3.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97</t>
   </si>
   <si>
     <t xml:space="preserve">1.00</t>
@@ -50,118 +50,79 @@
     <t xml:space="preserve">Penrith Panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42</t>
+    <t xml:space="preserve">4.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08</t>
+    <t xml:space="preserve">6.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76</t>
   </si>
   <si>
     <t xml:space="preserve">Cronulla Sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54</t>
+    <t xml:space="preserve">16.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Sydney Rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.11</t>
   </si>
   <si>
     <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
-    <t xml:space="preserve">33.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Sydney Rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.46</t>
+    <t xml:space="preserve">41.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.97</t>
   </si>
   <si>
     <t xml:space="preserve">NQ Cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">153.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58</t>
+    <t xml:space="preserve">117.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canberra Raiders</t>
   </si>
   <si>
     <t xml:space="preserve">Canterbury Bulldogs</t>
   </si>
   <si>
-    <t xml:space="preserve">194.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56</t>
+    <t xml:space="preserve">Gold Coast Titans</t>
   </si>
   <si>
     <t xml:space="preserve">Manly Sea Eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">833.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canberra Raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Coast Titans</t>
   </si>
   <si>
     <t xml:space="preserve">Melbourne Storm</t>
@@ -581,7 +542,7 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -592,16 +553,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -612,16 +573,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -632,13 +593,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -652,87 +613,87 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -752,7 +713,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -772,7 +733,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -792,7 +753,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -812,7 +773,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -832,7 +793,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -852,7 +813,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">Team</t>
   </si>
@@ -35,10 +35,10 @@
     <t xml:space="preserve">New Zealand Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97</t>
+    <t xml:space="preserve">3.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99</t>
   </si>
   <si>
     <t xml:space="preserve">1.00</t>
@@ -50,64 +50,73 @@
     <t xml:space="preserve">Penrith Panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26</t>
+    <t xml:space="preserve">4.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27</t>
   </si>
   <si>
     <t xml:space="preserve">Dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66</t>
+    <t xml:space="preserve">5.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76</t>
+    <t xml:space="preserve">6.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10</t>
   </si>
   <si>
     <t xml:space="preserve">Cronulla Sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">16.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64</t>
+    <t xml:space="preserve">13.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53</t>
   </si>
   <si>
     <t xml:space="preserve">South Sydney Rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">31.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.11</t>
+    <t xml:space="preserve">29.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.35</t>
   </si>
   <si>
     <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
-    <t xml:space="preserve">41.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.97</t>
+    <t xml:space="preserve">42.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.14</t>
   </si>
   <si>
     <t xml:space="preserve">NQ Cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">117.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.41</t>
+    <t xml:space="preserve">108.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.55</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
@@ -542,7 +551,7 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -553,16 +562,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -573,16 +582,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -593,13 +602,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -613,13 +622,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -633,13 +642,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -653,7 +662,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -673,7 +682,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -693,7 +702,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -713,7 +722,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -733,7 +742,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -753,7 +762,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -773,7 +782,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -793,7 +802,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -813,7 +822,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Team</t>
   </si>
@@ -35,10 +35,10 @@
     <t xml:space="preserve">New Zealand Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99</t>
+    <t xml:space="preserve">3.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97</t>
   </si>
   <si>
     <t xml:space="preserve">1.00</t>
@@ -50,73 +50,64 @@
     <t xml:space="preserve">Penrith Panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27</t>
+    <t xml:space="preserve">3.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14</t>
   </si>
   <si>
     <t xml:space="preserve">Dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05</t>
+    <t xml:space="preserve">5.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10</t>
+    <t xml:space="preserve">7.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23</t>
   </si>
   <si>
     <t xml:space="preserve">Cronulla Sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">13.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53</t>
+    <t xml:space="preserve">16.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66</t>
   </si>
   <si>
     <t xml:space="preserve">South Sydney Rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">29.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.35</t>
+    <t xml:space="preserve">19.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54</t>
   </si>
   <si>
     <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
-    <t xml:space="preserve">42.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.14</t>
+    <t xml:space="preserve">39.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.23</t>
   </si>
   <si>
     <t xml:space="preserve">NQ Cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">108.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.55</t>
+    <t xml:space="preserve">130.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.10</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
@@ -551,7 +542,7 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -562,16 +553,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -582,16 +573,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -602,13 +593,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -622,13 +613,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -642,13 +633,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -662,7 +653,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -682,7 +673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -702,7 +693,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -722,7 +713,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -742,7 +733,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -762,7 +753,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -782,7 +773,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -802,7 +793,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -822,7 +813,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
